--- a/docentes/Molina Quezada Raúl - Estadisticos 20222.xlsx
+++ b/docentes/Molina Quezada Raúl - Estadisticos 20222.xlsx
@@ -614,16 +614,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>9.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -637,16 +640,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H3">
+        <v>9.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -757,7 +763,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -783,7 +789,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">

--- a/docentes/Molina Quezada Raúl - Estadisticos 20222.xlsx
+++ b/docentes/Molina Quezada Raúl - Estadisticos 20222.xlsx
@@ -666,16 +666,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>8.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -689,16 +692,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -815,7 +821,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -841,7 +847,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Molina Quezada Raúl - Estadisticos 20222.xlsx
+++ b/docentes/Molina Quezada Raúl - Estadisticos 20222.xlsx
@@ -769,7 +769,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -795,7 +795,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -821,7 +821,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -847,7 +847,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
